--- a/2.tAK_fSK_双(有CRLF).xlsx
+++ b/2.tAK_fSK_双(有CRLF).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\测试样本\Ak-test\文档文件\Excel文件\xlsx - 副本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3526437E-EBD8-4DEC-95A3-F2C536FF350A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C0243E9-0E70-4DC6-A2D6-96AA52391136}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13120" xr2:uid="{9AC9544D-5DAE-6840-867E-D9890B3CE40D}"/>
   </bookViews>
@@ -37,11 +37,12 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
-    <t>accesskey=1NvihL8mdfL8piR8iqNTVCQWrXUEOf</t>
+    <t xml:space="preserve">accessID=LTAI5tEt2c8By9hQ7p9qBKrQ
+</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">accessID=LTAI5tEt2c8By9hQ7p9qBKrQ
+    <t xml:space="preserve">accesskey=1NvihL8mdfL8piR8iqNTVCQWrXUEOf
 </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -418,12 +419,12 @@
   <sheetData>
     <row r="1" spans="1:1" ht="31" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>0</v>
+    <row r="2" spans="1:1" ht="31" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
